--- a/New_Orleans_Pelicans_2025-26_stats.xlsx
+++ b/New_Orleans_Pelicans_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,6 +1186,66 @@
       </c>
       <c r="R12" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1199,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,6 +2012,66 @@
       </c>
       <c r="R12" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1965,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2718,6 +2838,66 @@
       </c>
       <c r="R12" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2731,7 +2911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3483,6 +3663,66 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3529,7 +3769,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.45454545454545</v>
+        <v>19.83333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3549,7 +3789,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>14.41666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3559,7 +3799,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.63636363636364</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="7">
@@ -3569,7 +3809,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.72727272727273</v>
+        <v>10.58333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3579,7 +3819,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.18181818181818</v>
+        <v>10.41666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -3589,7 +3829,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.7</v>
+        <v>6.818181818181818</v>
       </c>
     </row>
     <row r="10">
@@ -3599,23 +3839,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.5</v>
+        <v>5.571428571428571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Karlo Matković</t>
+          <t>DeAndre Jordan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.555555555555555</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DeAndre Jordan</t>
+          <t>Karlo Matković</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3629,7 +3869,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>3.909090909090909</v>
       </c>
     </row>
     <row r="14">
@@ -3639,7 +3879,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2.857142857142857</v>
       </c>
     </row>
     <row r="15">
@@ -3659,7 +3899,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="17">
@@ -3711,21 +3951,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.727272727272727</v>
+        <v>3.428571428571428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.428571428571428</v>
+        <v>3.416666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -3735,7 +3975,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.090909090909091</v>
+        <v>3.083333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3745,7 +3985,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6</v>
+        <v>2.545454545454545</v>
       </c>
     </row>
     <row r="7">
@@ -3755,7 +3995,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.454545454545455</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -3765,7 +4005,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.090909090909091</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3775,7 +4015,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.636363636363636</v>
+        <v>2.083333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3785,7 +4025,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.5</v>
+        <v>1.571428571428571</v>
       </c>
     </row>
     <row r="11">
@@ -3795,7 +4035,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.166666666666667</v>
+        <v>1.142857142857143</v>
       </c>
     </row>
     <row r="12">
@@ -3815,23 +4055,23 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karlo Matković</t>
+          <t>Jordan Hawkins</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jordan Hawkins</t>
+          <t>Karlo Matković</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3891,7 +4131,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.818181818181818</v>
+        <v>6.833333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3911,47 +4151,47 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.636363636363637</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>DeAndre Jordan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DeAndre Jordan</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4.857142857142857</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kevon Looney</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5</v>
+        <v>4.583333333333333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Kevon Looney</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.363636363636363</v>
+        <v>3.857142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -3961,7 +4201,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.636363636363636</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="10">
@@ -3971,7 +4211,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.818181818181818</v>
+        <v>2.916666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3981,47 +4221,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6</v>
+        <v>2.545454545454545</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Micah Peavy</t>
+          <t>Karlo Matković</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.571428571428572</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karlo Matković</t>
+          <t>Micah Peavy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.444444444444445</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Jordan Hawkins</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.714285714285714</v>
+        <v>1.727272727272727</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jordan Hawkins</t>
+          <t>Jordan Poole</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6</v>
+        <v>1.714285714285714</v>
       </c>
     </row>
     <row r="16">
@@ -4087,7 +4327,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.818181818181818</v>
+        <v>2.833333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -4097,7 +4337,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.090909090909091</v>
+        <v>2.166666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -4107,7 +4347,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.909090909090909</v>
+        <v>1.833333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -4117,7 +4357,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>1.545454545454545</v>
       </c>
     </row>
     <row r="7">
@@ -4127,7 +4367,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.181818181818182</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="8">
@@ -4137,7 +4377,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="9">
@@ -4147,7 +4387,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -4157,7 +4397,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="11">
@@ -4167,7 +4407,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="12">
@@ -4177,7 +4417,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -4241,7 +4481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4502,6 +4742,27 @@
         <v>242</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>104</v>
+      </c>
+      <c r="D13" t="n">
+        <v>118</v>
+      </c>
+      <c r="E13" t="n">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
